--- a/output/graficos_dimensiones/comunal_e_basbrut_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_basbrut_a_2023_valparaiso.xlsx
@@ -141,12 +141,12 @@
     <t xml:space="preserve">El Quisco</t>
   </si>
   <si>
+    <t xml:space="preserve">Calera</t>
+  </si>
+  <si>
     <t xml:space="preserve">Llaillay</t>
   </si>
   <si>
-    <t xml:space="preserve">Calera</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:23</t>
+    <t xml:space="preserve">2026-09-10 00:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1198,7 +1198,7 @@
         <v>41</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>5703</v>
+        <v>5502</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -1211,7 +1211,7 @@
         <v>42</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>5502</v>
+        <v>5703</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_basbrut_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_basbrut_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:28</t>
+    <t xml:space="preserve">2026-09-18 10:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
